--- a/outputs/reports/easy_ensemble/feature_importance_top10.xlsx
+++ b/outputs/reports/easy_ensemble/feature_importance_top10.xlsx
@@ -470,19 +470,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.2354919926285472</v>
+        <v>0.2770684556012389</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06181358361811956</v>
+        <v>0.0551125459600037</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=23.55%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=27.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -506,19 +506,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1389882420120957</v>
+        <v>0.1703274904421835</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03648260488033528</v>
+        <v>0.03388036947358997</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=13.90%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=17.03%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -542,19 +542,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1307135255794641</v>
+        <v>0.1166684700281321</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03431059949528809</v>
+        <v>0.02320688727468401</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=13.07%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=11.67%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BIZCT_PYHWY_AMT</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>사업비자부담금액</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.09743296908661454</v>
+        <v>0.1080844694510566</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02557488649432327</v>
+        <v>0.02149941709263758</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=9.74%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=10.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.09413657954162016</v>
+        <v>0.09138534227800571</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02470962713453345</v>
+        <v>0.01817774190655552</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=9.41%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=9.14%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -650,19 +650,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.09272458276014207</v>
+        <v>0.06511938252903433</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02433899635364706</v>
+        <v>0.01295309837682734</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=9.27%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.51%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -686,19 +686,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>BIZ_ENFC_ZON_DV_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>사업시행지역구분코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.07495003504036123</v>
+        <v>0.06332503787059059</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01967340887660712</v>
+        <v>0.01259617971482385</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=7.50%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=6.33%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.05975030498092234</v>
+        <v>0.040269061530693</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01568367752941874</v>
+        <v>0.008010043942247358</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.98%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.03%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.02560282399356293</v>
+        <v>0.02744716150905338</v>
       </c>
       <c r="F10" t="n">
-        <v>0.006720408129895161</v>
+        <v>0.00545960003587137</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=2.56%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=2.74%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TMNT_INDV_BZR_CLT_NUM</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>당월개인사업자거래처수</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.009094920445401911</v>
+        <v>0.01709586669552097</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002387298265120907</v>
+        <v>0.00340059187516828</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 당월개인사업자거래처수(TMNT_INDV_BZR_CLT_NUM). 기여도(정규화 비중)=0.91%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=1.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
